--- a/src/main/R/results-analysis_Siemensbahn.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn.xlsx
@@ -433,11 +433,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SiBa_v1</t>
+          <t>Siemensbahn+v1</t>
         </is>
       </c>
       <c r="B4">
         <v>577042817.9558327</v>
+      </c>
+      <c r="C4">
+        <v>27915089.2804002</v>
       </c>
       <c r="D4">
         <v>277436.0786111111</v>
@@ -452,11 +455,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SiBa_v2</t>
+          <t>Siemensbahn+v2</t>
         </is>
       </c>
       <c r="B5">
         <v>576954629.6421262</v>
+      </c>
+      <c r="C5">
+        <v>27805258.96553729</v>
       </c>
       <c r="D5">
         <v>277845.8266666667</v>

--- a/src/main/R/results-analysis_Siemensbahn.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn.xlsx
@@ -1,21 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Lima\Documents\TUB\Studium\Masterarbeit_git\matsim-berlin\src\main\R\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{AE9FCC89-F9E5-43BE-AF00-4B139FEDA880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-4935" yWindow="-15870" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={736561BD-4D1A-4791-81D1-0A00765B182F}</author>
+  </authors>
+  <commentList>
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{736561BD-4D1A-4791-81D1-0A00765B182F}">
+      <text>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Total Travel Time in Car in Base Case for these Agents: 10.790 hours</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Total Monetized Score [EUR/day]</t>
+  </si>
+  <si>
+    <t>Total Monetized Score Delimited Region [EUR/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time for PT-Users [h/day]</t>
+  </si>
+  <si>
+    <t>Total Transfers [1/day]</t>
+  </si>
+  <si>
+    <t>Total Car-km [km/day]</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Siemensbahn</t>
+  </si>
+  <si>
+    <t>Siemensbahn+v1</t>
+  </si>
+  <si>
+    <t>Siemensbahn+v2</t>
+  </si>
+  <si>
+    <t>Diff to Base Case [EUR/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time in PT for Former Car-Users in Base Case [h/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time for Remaining PT-Users from Base Case [h/day]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -31,16 +116,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,28 +164,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Eduardo de Almeida Lima" id="{CA880B87-2CD4-432E-A584-C6664854B856}" userId="9a31f4cde4da338c" providerId="Windows Live"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +263,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +297,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +332,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -349,132 +507,175 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G3" dT="2025-08-28T11:41:42.92" personId="{CA880B87-2CD4-432E-A584-C6664854B856}" id="{736561BD-4D1A-4791-81D1-0A00765B182F}">
+    <text>Total Travel Time in Car in Base Case for these Agents: 10.790 hours</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="10" width="18.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total Monetized Score [EUR/day]</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total Monetized Score Delimited Region [EUR/day]</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Travel Time for PT-Users [h/day]</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total Transfers [1/day]</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total Car-km [km/day]</t>
-        </is>
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Base Case</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>576849472.0814978</v>
-      </c>
-      <c r="C2">
-        <v>27597046.52457722</v>
-      </c>
-      <c r="D2">
-        <v>277740.8855555556</v>
-      </c>
-      <c r="E2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4">
+        <v>576849472.08149779</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4">
+        <v>27597046.524577219</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="8">
+        <v>277740.88555555558</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="6">
         <v>267032</v>
       </c>
-      <c r="F2">
-        <v>4432706.52</v>
+      <c r="J2" s="6">
+        <v>4432706.5199999996</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Siemensbahn</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>576853479.8857567</v>
-      </c>
-      <c r="C3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4">
+        <v>576853479.88575673</v>
+      </c>
+      <c r="C3" s="4">
+        <f>B3-B$2</f>
+        <v>4007.8042589426041</v>
+      </c>
+      <c r="D3" s="4">
         <v>27738560.02270747</v>
       </c>
-      <c r="D3">
-        <v>277881.3969444445</v>
-      </c>
-      <c r="E3">
+      <c r="E3" s="4">
+        <f>D3-D$2</f>
+        <v>141513.49813025072</v>
+      </c>
+      <c r="F3" s="7">
+        <v>277881.39694444451</v>
+      </c>
+      <c r="G3" s="7">
+        <v>10212</v>
+      </c>
+      <c r="H3" s="9">
+        <v>269152</v>
+      </c>
+      <c r="I3" s="6">
         <v>266906</v>
       </c>
-      <c r="F3">
+      <c r="J3" s="6">
         <v>4428922.84</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Siemensbahn+v1</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>577042817.9558327</v>
-      </c>
-      <c r="C4">
-        <v>27915089.2804002</v>
-      </c>
-      <c r="D4">
-        <v>277436.0786111111</v>
-      </c>
-      <c r="E4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>577042817.95583272</v>
+      </c>
+      <c r="C4" s="4">
+        <f>B4-B$2</f>
+        <v>193345.87433493137</v>
+      </c>
+      <c r="D4" s="4">
+        <v>27915089.280400202</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" ref="C4:E5" si="0">D4-D$2</f>
+        <v>318042.75582298264</v>
+      </c>
+      <c r="F4" s="6">
+        <v>277436.07861111109</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6">
         <v>265978</v>
       </c>
-      <c r="F4">
-        <v>4435347.999</v>
+      <c r="J4" s="6">
+        <v>4435347.9989999998</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Siemensbahn+v2</t>
-        </is>
-      </c>
-      <c r="B5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4">
         <v>576954629.6421262</v>
       </c>
-      <c r="C5">
-        <v>27805258.96553729</v>
-      </c>
-      <c r="D5">
-        <v>277845.8266666667</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="4">
+        <f t="shared" si="0"/>
+        <v>105157.56062841415</v>
+      </c>
+      <c r="D5" s="4">
+        <v>27805258.965537291</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="0"/>
+        <v>208212.44096007198</v>
+      </c>
+      <c r="F5" s="6">
+        <v>277845.82666666672</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6">
         <v>266274</v>
       </c>
-      <c r="F5">
+      <c r="J5" s="6">
         <v>4437178.284</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/main/R/results-analysis_Siemensbahn.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,25 +362,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total Monetized Score [EUR/day]</t>
+          <t>Total Monetized Score Delimited Region [EUR/day]</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Total Monetized Score Delimited Region [EUR/day]</t>
+          <t>Total Travel Time for PT-Users [h/day]</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Total Travel Time for PT-Users [h/day]</t>
+          <t>Total Transfers [1/day]</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total Transfers [1/day]</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Car-km [km/day]</t>
         </is>
@@ -393,19 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>577758076.2797799</v>
+        <v>21122548.0872282</v>
       </c>
       <c r="C2">
-        <v>21808131.96895123</v>
+        <v>138136.0972222222</v>
       </c>
       <c r="D2">
-        <v>276979.0491666667</v>
+        <v>153750</v>
       </c>
       <c r="E2">
-        <v>266913</v>
-      </c>
-      <c r="F2">
-        <v>4514604.345</v>
+        <v>1979394.16</v>
       </c>
     </row>
     <row r="3">
@@ -415,19 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>577686297.2583973</v>
+        <v>21133550.90304748</v>
       </c>
       <c r="C3">
-        <v>21827838.55077017</v>
+        <v>140969.8083333333</v>
       </c>
       <c r="D3">
-        <v>277538.0641666666</v>
+        <v>152430</v>
       </c>
       <c r="E3">
-        <v>266953</v>
-      </c>
-      <c r="F3">
-        <v>4508901.715</v>
+        <v>1941973.24</v>
       </c>
     </row>
     <row r="4">
@@ -437,19 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>577792258.8360479</v>
+        <v>21156219.49181719</v>
       </c>
       <c r="C4">
-        <v>21847699.31854214</v>
+        <v>142385.475</v>
       </c>
       <c r="D4">
-        <v>277636.7913888889</v>
+        <v>149870</v>
       </c>
       <c r="E4">
-        <v>266886</v>
-      </c>
-      <c r="F4">
-        <v>4507408.865</v>
+        <v>1911768.38</v>
       </c>
     </row>
     <row r="5">
@@ -459,19 +445,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>577830827.1462517</v>
+        <v>21147884.81078412</v>
       </c>
       <c r="C5">
-        <v>21844314.12200892</v>
+        <v>142601.1638888889</v>
       </c>
       <c r="D5">
-        <v>277445.6319444444</v>
+        <v>149800</v>
       </c>
       <c r="E5">
-        <v>266531</v>
-      </c>
-      <c r="F5">
-        <v>4513263.796</v>
+        <v>1914024.07</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/R/results-analysis_Siemensbahn.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,10 +372,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Total Travel Distance for PT-Users [km/day]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total Transfers [1/day]</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Car-km [km/day]</t>
         </is>
@@ -394,9 +399,12 @@
         <v>138136.0972222222</v>
       </c>
       <c r="D2">
+        <v>2256073.41</v>
+      </c>
+      <c r="E2">
         <v>153750</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1979394.16</v>
       </c>
     </row>
@@ -413,9 +421,12 @@
         <v>140969.8083333333</v>
       </c>
       <c r="D3">
+        <v>2316893.95</v>
+      </c>
+      <c r="E3">
         <v>152430</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1941973.24</v>
       </c>
     </row>
@@ -432,9 +443,12 @@
         <v>142385.475</v>
       </c>
       <c r="D4">
+        <v>2344499.19</v>
+      </c>
+      <c r="E4">
         <v>149870</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1911768.38</v>
       </c>
     </row>
@@ -451,9 +465,12 @@
         <v>142601.1638888889</v>
       </c>
       <c r="D5">
+        <v>2338632.79</v>
+      </c>
+      <c r="E5">
         <v>149800</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>1914024.07</v>
       </c>
     </row>

--- a/src/main/R/results-analysis_Siemensbahn.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn.xlsx
@@ -1,21 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Lima\Documents\TUB\Studium\Masterarbeit_git\matsim-berlin\src\main\R\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD81AB2-0BBD-400C-98C4-D14E8314960F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Total Monetized Score Delimited Region [EUR/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time for PT-Users [h/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Distance for PT-Users [km/day]</t>
+  </si>
+  <si>
+    <t>Total Transfers [1/day]</t>
+  </si>
+  <si>
+    <t>Total Car-km [km/day]</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Siemensbahn</t>
+  </si>
+  <si>
+    <t>Delta [EUR/day]</t>
+  </si>
+  <si>
+    <t>Siemensbahn+V1</t>
+  </si>
+  <si>
+    <t>Siemensbahn+V2</t>
+  </si>
+  <si>
+    <t>Delta [h/day]</t>
+  </si>
+  <si>
+    <t>Delta [km/day]</t>
+  </si>
+  <si>
+    <t>Mean Travel Distance for PT-Users [km/day]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -31,16 +97,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,28 +133,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +221,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +255,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +290,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,131 +466,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" style="3" customWidth="1"/>
+    <col min="2" max="5" width="28.5703125" style="3" hidden="1" customWidth="1"/>
+    <col min="6" max="9" width="28.5703125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="21.140625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total Monetized Score Delimited Region [EUR/day]</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total Travel Time for PT-Users [h/day]</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Travel Distance for PT-Users [km/day]</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total Transfers [1/day]</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total Car-km [km/day]</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Base Case</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>21122548.0872282</v>
-      </c>
-      <c r="C2">
-        <v>138136.0972222222</v>
-      </c>
-      <c r="D2">
-        <v>2256073.41</v>
-      </c>
-      <c r="E2">
-        <v>153750</v>
-      </c>
-      <c r="F2">
-        <v>1979394.16</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5">
+        <v>34571122.147855841</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="5">
+        <v>232421.50277777779</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="5">
+        <v>3974066.18</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="5">
+        <v>262510</v>
+      </c>
+      <c r="K2" s="5">
+        <v>3117796.79</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Siemensbahn</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>21133550.90304748</v>
-      </c>
-      <c r="C3">
-        <v>140969.8083333333</v>
-      </c>
-      <c r="D3">
-        <v>2316893.95</v>
-      </c>
-      <c r="E3">
-        <v>152430</v>
-      </c>
-      <c r="F3">
-        <v>1941973.24</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>34582072.368908137</v>
+      </c>
+      <c r="C3" s="5">
+        <f t="shared" ref="C3:I5" si="0">B3-B$2</f>
+        <v>10950.22105229646</v>
+      </c>
+      <c r="D3" s="5">
+        <v>234691.4666666667</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" si="0"/>
+        <v>2269.9638888889167</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4026098.48</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" si="0"/>
+        <v>52032.299999999814</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>260510</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3085751.61</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Siemensbahn+v1</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>21156219.49181719</v>
-      </c>
-      <c r="C4">
-        <v>142385.475</v>
-      </c>
-      <c r="D4">
-        <v>2344499.19</v>
-      </c>
-      <c r="E4">
-        <v>149870</v>
-      </c>
-      <c r="F4">
-        <v>1911768.38</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34606654.219710387</v>
+      </c>
+      <c r="C4" s="5">
+        <f t="shared" si="0"/>
+        <v>35532.071854546666</v>
+      </c>
+      <c r="D4" s="5">
+        <v>236038.79166666669</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>3617.2888888888992</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4052065.81</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>77999.629999999888</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>257890</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3058709.49</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Siemensbahn+v2</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>21147884.81078412</v>
-      </c>
-      <c r="C5">
-        <v>142601.1638888889</v>
-      </c>
-      <c r="D5">
-        <v>2338632.79</v>
-      </c>
-      <c r="E5">
-        <v>149800</v>
-      </c>
-      <c r="F5">
-        <v>1914024.07</v>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5">
+        <v>34599049.779677667</v>
+      </c>
+      <c r="C5" s="5">
+        <f t="shared" si="0"/>
+        <v>27927.6318218261</v>
+      </c>
+      <c r="D5" s="5">
+        <v>237194.7027777778</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>4773.2000000000116</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4060263</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="0"/>
+        <v>86196.819999999832</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>258060</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3041458.76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>